--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:15:57+00:00</t>
+    <t>2026-09-14T12:52:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:52:13+00:00</t>
+    <t>2026-09-14T13:01:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:01:52+00:00</t>
+    <t>2026-09-14T13:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.36--20230331232804.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:11:56+00:00</t>
+    <t>2026-09-14T13:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
